--- a/02_Zero_Shot/outputs/NLI/roberta-large-mnli/RESULT_pan_roberta-large-mnli_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/roberta-large-mnli/RESULT_pan_roberta-large-mnli_zeroshot.xlsx
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.63783648899971</v>
+        <v>83.67972960999759</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04290491833740986</v>
+        <v>0.06020124432373928</v>
       </c>
     </row>
   </sheetData>
